--- a/06_AUDITORIA_Y_VALIDACION/Matriz_Errores.xlsx
+++ b/06_AUDITORIA_Y_VALIDACION/Matriz_Errores.xlsx
@@ -1849,7 +1849,7 @@
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
-          <t>historial/etapa1_auditoria_v2_0/verificacion</t>
+          <t>Evidencias_Validacion/etapa1_auditoria (verificación de la etapa 1)</t>
         </is>
       </c>
     </row>
